--- a/EKG_Kalite_Yönetim_Sistemi/09_Risk Azaltma ve PFMEA/01_RR1 - PFMEA ve Müşteri Puanlama Kuralları/EKG-PRJ-FRM-32_stellantis_pfmea_sentez_sablonu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/09_Risk Azaltma ve PFMEA/01_RR1 - PFMEA ve Müşteri Puanlama Kuralları/EKG-PRJ-FRM-32_stellantis_pfmea_sentez_sablonu.xlsx
@@ -941,7 +941,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-32&amp;C&amp;"Arial,Regular"&amp;11Stellantis PFMEA Sentez Şablonu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 23.09.2026
+Revizyon nedeni: PFMEA sentezi ve aksiyon/onay kanıtı ayrıldı; kaynaklandırılmamış uyum iddiası kaldırıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1122,7 +1123,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-32&amp;C&amp;"Arial,Regular"&amp;11Stellantis PFMEA Sentez Şablonu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 23.09.2026
+Revizyon nedeni: PFMEA sentezi ve aksiyon/onay kanıtı ayrıldı; kaynaklandırılmamış uyum iddiası kaldırıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>